--- a/artfynd/A 4006-2024 artfynd.xlsx
+++ b/artfynd/A 4006-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4006-2024 artfynd.xlsx
+++ b/artfynd/A 4006-2024 artfynd.xlsx
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66412587</v>
+        <v>17148850</v>
       </c>
       <c r="B2" t="n">
-        <v>87429</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5581</v>
+        <v>232052</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulfotsskölding</t>
+          <t>Mörkstiftig hällfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pluteus romellii</t>
+          <t>Hieracium sublividum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Britzelm.) Sacc.</t>
+          <t>(Dahlst.) Johanss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kävelsbo NV, Ög</t>
+          <t>Åtvid socken, 400 m NV Kävelsbo, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562986.8908847028</v>
+        <v>563060</v>
       </c>
       <c r="R2" t="n">
-        <v>6454644.991325353</v>
+        <v>6454736</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-06-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Collector Tommy Nilsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,24 +759,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gräsmark; vägkant</t>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>4183, 1772503</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Via Anders Svenson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 4006-2024 artfynd.xlsx
+++ b/artfynd/A 4006-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,8 +794,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17148850</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>